--- a/aisan_lbo_case/docs/AISAN_4667_LBO_Model.xlsx
+++ b/aisan_lbo_case/docs/AISAN_4667_LBO_Model.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Financing structure</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference share price (¥, post-fraud-news)</t>
+    <t xml:space="preserve">Reference share price (¥, post-investigation disclosure)</t>
   </si>
   <si>
     <t xml:space="preserve">5-Jun-26 close</t>
@@ -789,7 +789,7 @@
     <t xml:space="preserve">Exit EBITDA (¥mm)</t>
   </si>
   <si>
-    <t xml:space="preserve">Base: mid-single-digit growth, gradual margin lift to 12% via mix &amp; cost discipline; exit 10x. Returns improve after treasury-share correction but remain below a clean 20% hurdle.</t>
+    <t xml:space="preserve">Base: mid-single-digit growth, gradual margin lift to 12% via mix &amp; cost discipline; exit 10x; returns remain below a clean 20% hurdle.</t>
   </si>
   <si>
     <t xml:space="preserve">Exit EV/EBITDA</t>
